--- a/Operator_Guides/Connector_Program_Project_Plan.xlsx
+++ b/Operator_Guides/Connector_Program_Project_Plan.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Assumptions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Plan'!$A$1:$K$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Project Plan'!$A$1:$L$137</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,9 +19,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="dd-mmm-yy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yy"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -128,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -139,7 +138,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -148,7 +147,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -157,7 +156,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -166,7 +165,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,7 +174,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,7 +183,7 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -193,7 +192,7 @@
     <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,6 +207,48 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -573,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:L137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -587,6 +628,7 @@
     <col width="26" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,6 +687,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>% Complete</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
@@ -661,10 +708,10 @@
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="29" t="n">
         <v>46251</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="29" t="n">
         <v>46451</v>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
@@ -676,6 +723,9 @@
           <t>Mobilisation is the long pole</t>
         </is>
       </c>
+      <c r="L2" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n">
@@ -694,10 +744,10 @@
       <c r="D3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E3" s="7" t="n">
+      <c r="E3" s="31" t="n">
         <v>46251</v>
       </c>
-      <c r="F3" s="7" t="n">
+      <c r="F3" s="31" t="n">
         <v>46262</v>
       </c>
       <c r="G3" s="5" t="inlineStr"/>
@@ -717,6 +767,9 @@
           <t>Salesforce connector DEFERRED — BDH carries Salesforce data</t>
         </is>
       </c>
+      <c r="L3" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="n">
@@ -735,10 +788,10 @@
       <c r="D4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="33" t="n">
         <v>46265</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="33" t="n">
         <v>46267</v>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -757,7 +810,14 @@
           <t>Sponsor/Business</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr"/>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>Architecture as delivered: ONE shared Connector.Chassis project (v1.18.0) referenced by all five connectors; 9 of 23 chassis modules fully shared, 67 declared per-connector divergences (see 8.5)</t>
+        </is>
+      </c>
+      <c r="L4" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="n">
@@ -776,10 +836,10 @@
       <c r="D5" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="35" t="n">
         <v>46265</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="35" t="n">
         <v>46286</v>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -803,6 +863,9 @@
         </is>
       </c>
       <c r="K5" s="12" t="inlineStr"/>
+      <c r="L5" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="n">
@@ -821,10 +884,10 @@
       <c r="D6" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="35" t="n">
         <v>46287</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="35" t="n">
         <v>46315</v>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -851,6 +914,9 @@
         <is>
           <t>Interim dev capacity until hire lands</t>
         </is>
+      </c>
+      <c r="L6" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -870,10 +936,10 @@
       <c r="D7" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="35" t="n">
         <v>46287</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="35" t="n">
         <v>46300</v>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -897,6 +963,9 @@
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr"/>
+      <c r="L7" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="n">
@@ -915,10 +984,10 @@
       <c r="D8" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="35" t="n">
         <v>46301</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="35" t="n">
         <v>46344</v>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -942,6 +1011,9 @@
         </is>
       </c>
       <c r="K8" s="12" t="inlineStr"/>
+      <c r="L8" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="n">
@@ -960,10 +1032,10 @@
       <c r="D9" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="35" t="n">
         <v>46345</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="35" t="n">
         <v>46437</v>
       </c>
       <c r="G9" s="11" t="inlineStr">
@@ -986,6 +1058,9 @@
         <is>
           <t>Typical 2-3 month notice</t>
         </is>
+      </c>
+      <c r="L9" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1005,10 +1080,10 @@
       <c r="D10" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="35" t="n">
         <v>46440</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="35" t="n">
         <v>46451</v>
       </c>
       <c r="G10" s="11" t="inlineStr">
@@ -1032,6 +1107,9 @@
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr"/>
+      <c r="L10" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="n">
@@ -1050,10 +1128,10 @@
       <c r="D11" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="35" t="n">
         <v>46287</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="35" t="n">
         <v>46300</v>
       </c>
       <c r="G11" s="11" t="inlineStr">
@@ -1077,6 +1155,9 @@
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr"/>
+      <c r="L11" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="n">
@@ -1095,10 +1176,10 @@
       <c r="D12" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="35" t="n">
         <v>46301</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="F12" s="35" t="n">
         <v>46315</v>
       </c>
       <c r="G12" s="11" t="inlineStr">
@@ -1122,6 +1203,9 @@
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr"/>
+      <c r="L12" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="n">
@@ -1140,10 +1224,10 @@
       <c r="D13" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="35" t="n">
         <v>46265</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="F13" s="35" t="n">
         <v>46279</v>
       </c>
       <c r="G13" s="11" t="inlineStr">
@@ -1170,6 +1254,9 @@
         <is>
           <t>Clarizen, Seismic, Altrata, BDH</t>
         </is>
+      </c>
+      <c r="L13" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1189,10 +1276,10 @@
       <c r="D14" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="37" t="n">
         <v>46265</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="37" t="n">
         <v>46279</v>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -1216,6 +1303,9 @@
         </is>
       </c>
       <c r="K14" s="15" t="inlineStr"/>
+      <c r="L14" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="n">
@@ -1234,10 +1324,10 @@
       <c r="D15" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="E15" s="37" t="n">
         <v>46280</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="F15" s="37" t="n">
         <v>46286</v>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -1261,6 +1351,9 @@
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr"/>
+      <c r="L15" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="17" t="n">
@@ -1279,10 +1372,10 @@
       <c r="D16" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="19" t="n">
+      <c r="E16" s="39" t="n">
         <v>46265</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="39" t="n">
         <v>46267</v>
       </c>
       <c r="G16" s="17" t="inlineStr">
@@ -1306,6 +1399,9 @@
         </is>
       </c>
       <c r="K16" s="18" t="inlineStr"/>
+      <c r="L16" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1322,10 +1418,10 @@
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="29" t="n">
         <v>46265</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="29" t="n">
         <v>46358</v>
       </c>
       <c r="G17" s="2" t="inlineStr"/>
@@ -1337,6 +1433,9 @@
           <t>Parallel tracks, queue-bound</t>
         </is>
       </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="n">
@@ -1355,10 +1454,10 @@
       <c r="D18" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="35" t="n">
         <v>46265</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="35" t="n">
         <v>46279</v>
       </c>
       <c r="G18" s="11" t="inlineStr">
@@ -1382,6 +1481,9 @@
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr"/>
+      <c r="L18" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="n">
@@ -1400,10 +1502,10 @@
       <c r="D19" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="35" t="n">
         <v>46280</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="35" t="n">
         <v>46293</v>
       </c>
       <c r="G19" s="11" t="inlineStr">
@@ -1430,6 +1532,9 @@
         <is>
           <t>One app per connector</t>
         </is>
+      </c>
+      <c r="L19" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1449,10 +1554,10 @@
       <c r="D20" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E20" s="33" t="n">
         <v>46294</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F20" s="33" t="n">
         <v>46296</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
@@ -1472,6 +1577,9 @@
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr"/>
+      <c r="L20" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="n">
@@ -1490,10 +1598,10 @@
       <c r="D21" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="35" t="n">
         <v>46297</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="35" t="n">
         <v>46318</v>
       </c>
       <c r="G21" s="11" t="inlineStr">
@@ -1517,6 +1625,9 @@
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr"/>
+      <c r="L21" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
@@ -1535,10 +1646,10 @@
       <c r="D22" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E22" s="10" t="n">
+      <c r="E22" s="33" t="n">
         <v>46321</v>
       </c>
-      <c r="F22" s="10" t="n">
+      <c r="F22" s="33" t="n">
         <v>46325</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
@@ -1558,6 +1669,9 @@
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr"/>
+      <c r="L22" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="n">
@@ -1576,10 +1690,10 @@
       <c r="D23" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="35" t="n">
         <v>46287</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="35" t="n">
         <v>46308</v>
       </c>
       <c r="G23" s="11" t="inlineStr">
@@ -1603,6 +1717,9 @@
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr"/>
+      <c r="L23" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="n">
@@ -1621,10 +1738,10 @@
       <c r="D24" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="35" t="n">
         <v>46309</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="35" t="n">
         <v>46329</v>
       </c>
       <c r="G24" s="11" t="inlineStr">
@@ -1648,6 +1765,9 @@
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr"/>
+      <c r="L24" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="n">
@@ -1666,10 +1786,10 @@
       <c r="D25" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="35" t="n">
         <v>46309</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="35" t="n">
         <v>46329</v>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -1693,6 +1813,9 @@
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr"/>
+      <c r="L25" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="n">
@@ -1711,10 +1834,10 @@
       <c r="D26" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="35" t="n">
         <v>46280</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="35" t="n">
         <v>46300</v>
       </c>
       <c r="G26" s="11" t="inlineStr">
@@ -1738,6 +1861,9 @@
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr"/>
+      <c r="L26" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
@@ -1756,10 +1882,10 @@
       <c r="D27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E27" s="31" t="n">
         <v>46301</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F27" s="31" t="n">
         <v>46308</v>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -1779,6 +1905,9 @@
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr"/>
+      <c r="L27" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
@@ -1797,10 +1926,10 @@
       <c r="D28" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E28" s="10" t="n">
+      <c r="E28" s="33" t="n">
         <v>46309</v>
       </c>
-      <c r="F28" s="10" t="n">
+      <c r="F28" s="33" t="n">
         <v>46315</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
@@ -1820,6 +1949,9 @@
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr"/>
+      <c r="L28" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="14" t="n">
@@ -1838,10 +1970,10 @@
       <c r="D29" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E29" s="16" t="n">
+      <c r="E29" s="37" t="n">
         <v>46301</v>
       </c>
-      <c r="F29" s="16" t="n">
+      <c r="F29" s="37" t="n">
         <v>46315</v>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -1868,6 +2000,9 @@
         <is>
           <t>Clarizen + Seismic listeners</t>
         </is>
+      </c>
+      <c r="L29" s="38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1887,10 +2022,10 @@
       <c r="D30" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="10" t="n">
+      <c r="E30" s="33" t="n">
         <v>46316</v>
       </c>
-      <c r="F30" s="10" t="n">
+      <c r="F30" s="33" t="n">
         <v>46322</v>
       </c>
       <c r="G30" s="8" t="inlineStr">
@@ -1906,6 +2041,9 @@
       </c>
       <c r="J30" s="9" t="inlineStr"/>
       <c r="K30" s="9" t="inlineStr"/>
+      <c r="L30" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="n">
@@ -1924,10 +2062,10 @@
       <c r="D31" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="35" t="n">
         <v>46309</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="35" t="n">
         <v>46322</v>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -1951,6 +2089,9 @@
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr"/>
+      <c r="L31" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
@@ -1969,10 +2110,10 @@
       <c r="D32" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="E32" s="33" t="n">
         <v>46323</v>
       </c>
-      <c r="F32" s="10" t="n">
+      <c r="F32" s="33" t="n">
         <v>46329</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
@@ -1992,6 +2133,9 @@
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr"/>
+      <c r="L32" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="n">
@@ -2010,10 +2154,10 @@
       <c r="D33" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="35" t="n">
         <v>46309</v>
       </c>
-      <c r="F33" s="13" t="n">
+      <c r="F33" s="35" t="n">
         <v>46329</v>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -2037,6 +2181,9 @@
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr"/>
+      <c r="L33" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
@@ -2055,10 +2202,10 @@
       <c r="D34" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="33" t="n">
         <v>46330</v>
       </c>
-      <c r="F34" s="10" t="n">
+      <c r="F34" s="33" t="n">
         <v>46336</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
@@ -2078,6 +2225,9 @@
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr"/>
+      <c r="L34" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2096,10 +2246,10 @@
       <c r="D35" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E35" s="7" t="n">
+      <c r="E35" s="31" t="n">
         <v>46309</v>
       </c>
-      <c r="F35" s="7" t="n">
+      <c r="F35" s="31" t="n">
         <v>46311</v>
       </c>
       <c r="G35" s="5" t="inlineStr">
@@ -2119,6 +2269,9 @@
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr"/>
+      <c r="L35" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
@@ -2137,10 +2290,10 @@
       <c r="D36" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="33" t="n">
         <v>46316</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="33" t="n">
         <v>46329</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -2159,7 +2312,14 @@
           <t>DevOps/Windows Engineer</t>
         </is>
       </c>
-      <c r="K36" s="9" t="inlineStr"/>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>NOT STARTED — no release pipeline exists at the repository root today; the SBOM/signing/MSI designs sit in five per-connector workflow files GitHub never runs, and no release or tag has ever been produced</t>
+        </is>
+      </c>
+      <c r="L36" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="17" t="n">
@@ -2178,10 +2338,10 @@
       <c r="D37" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E37" s="19" t="n">
+      <c r="E37" s="39" t="n">
         <v>46268</v>
       </c>
-      <c r="F37" s="19" t="n">
+      <c r="F37" s="39" t="n">
         <v>46273</v>
       </c>
       <c r="G37" s="17" t="inlineStr">
@@ -2200,7 +2360,14 @@
         </is>
       </c>
       <c r="J37" s="18" t="inlineStr"/>
-      <c r="K37" s="18" t="inlineStr"/>
+      <c r="K37" s="18" t="inlineStr">
+        <is>
+          <t>TOGAF concerns 3-7 from the architecture assessment are still open at submission</t>
+        </is>
+      </c>
+      <c r="L37" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="17" t="n">
@@ -2219,10 +2386,10 @@
       <c r="D38" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="19" t="n">
+      <c r="E38" s="39" t="n">
         <v>46295</v>
       </c>
-      <c r="F38" s="19" t="n">
+      <c r="F38" s="39" t="n">
         <v>46295</v>
       </c>
       <c r="G38" s="17" t="inlineStr">
@@ -2245,7 +2412,10 @@
           <t>Platform Lead &amp; Architect</t>
         </is>
       </c>
-      <c r="K38" s="18" t="inlineStr"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="17" t="n">
@@ -2264,10 +2434,10 @@
       <c r="D39" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E39" s="19" t="n">
+      <c r="E39" s="39" t="n">
         <v>46296</v>
       </c>
-      <c r="F39" s="19" t="n">
+      <c r="F39" s="39" t="n">
         <v>46302</v>
       </c>
       <c r="G39" s="17" t="inlineStr">
@@ -2287,6 +2457,9 @@
       </c>
       <c r="J39" s="18" t="inlineStr"/>
       <c r="K39" s="18" t="inlineStr"/>
+      <c r="L39" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="n">
@@ -2305,10 +2478,10 @@
       <c r="D40" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E40" s="16" t="n">
+      <c r="E40" s="37" t="n">
         <v>46297</v>
       </c>
-      <c r="F40" s="16" t="n">
+      <c r="F40" s="37" t="n">
         <v>46301</v>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2332,6 +2505,9 @@
         </is>
       </c>
       <c r="K40" s="15" t="inlineStr"/>
+      <c r="L40" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="n">
@@ -2350,10 +2526,10 @@
       <c r="D41" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="E41" s="37" t="n">
         <v>46324</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="F41" s="37" t="n">
         <v>46338</v>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -2377,6 +2553,9 @@
         </is>
       </c>
       <c r="K41" s="15" t="inlineStr"/>
+      <c r="L41" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="14" t="n">
@@ -2395,10 +2574,10 @@
       <c r="D42" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E42" s="16" t="n">
+      <c r="E42" s="37" t="n">
         <v>46339</v>
       </c>
-      <c r="F42" s="16" t="n">
+      <c r="F42" s="37" t="n">
         <v>46353</v>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -2422,6 +2601,9 @@
         </is>
       </c>
       <c r="K42" s="15" t="inlineStr"/>
+      <c r="L42" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="14" t="n">
@@ -2440,10 +2622,10 @@
       <c r="D43" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E43" s="16" t="n">
+      <c r="E43" s="37" t="n">
         <v>46356</v>
       </c>
-      <c r="F43" s="16" t="n">
+      <c r="F43" s="37" t="n">
         <v>46358</v>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -2463,6 +2645,9 @@
       </c>
       <c r="J43" s="15" t="inlineStr"/>
       <c r="K43" s="15" t="inlineStr"/>
+      <c r="L43" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
@@ -2483,10 +2668,10 @@
           <t>0 — milestone</t>
         </is>
       </c>
-      <c r="E44" s="22" t="n">
+      <c r="E44" s="41" t="n">
         <v>46338</v>
       </c>
-      <c r="F44" s="22" t="n">
+      <c r="F44" s="41" t="n">
         <v>46338</v>
       </c>
       <c r="G44" s="20" t="inlineStr">
@@ -2502,6 +2687,9 @@
       </c>
       <c r="J44" s="21" t="inlineStr"/>
       <c r="K44" s="21" t="inlineStr"/>
+      <c r="L44" s="42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -2518,10 +2706,10 @@
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="29" t="n">
         <v>46280</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="29" t="n">
         <v>46478</v>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -2533,6 +2721,9 @@
           <t>Pilot proves pattern: ACL trim, pen test, CAB route</t>
         </is>
       </c>
+      <c r="L45" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="n">
@@ -2551,10 +2742,10 @@
       <c r="D46" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="35" t="n">
         <v>46280</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="F46" s="35" t="n">
         <v>46293</v>
       </c>
       <c r="G46" s="11" t="inlineStr">
@@ -2581,6 +2772,9 @@
         <is>
           <t>Guide §10 checklist</t>
         </is>
+      </c>
+      <c r="L46" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -2600,10 +2794,10 @@
       <c r="D47" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="E47" s="37" t="n">
         <v>46294</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="F47" s="37" t="n">
         <v>46308</v>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -2630,6 +2824,9 @@
         <is>
           <t>config/exclusions.json</t>
         </is>
+      </c>
+      <c r="L47" s="38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -2649,10 +2846,10 @@
       <c r="D48" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="35" t="n">
         <v>46323</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="F48" s="35" t="n">
         <v>46329</v>
       </c>
       <c r="G48" s="11" t="inlineStr">
@@ -2676,6 +2873,9 @@
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr"/>
+      <c r="L48" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
@@ -2694,10 +2894,10 @@
       <c r="D49" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="7" t="n">
+      <c r="E49" s="31" t="n">
         <v>46339</v>
       </c>
-      <c r="F49" s="7" t="n">
+      <c r="F49" s="31" t="n">
         <v>46342</v>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -2717,6 +2917,9 @@
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr"/>
+      <c r="L49" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
@@ -2735,10 +2938,10 @@
       <c r="D50" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E50" s="10" t="n">
+      <c r="E50" s="33" t="n">
         <v>46343</v>
       </c>
-      <c r="F50" s="10" t="n">
+      <c r="F50" s="33" t="n">
         <v>46357</v>
       </c>
       <c r="G50" s="8" t="inlineStr">
@@ -2758,6 +2961,9 @@
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr"/>
+      <c r="L50" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
@@ -2776,10 +2982,10 @@
       <c r="D51" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E51" s="7" t="n">
+      <c r="E51" s="31" t="n">
         <v>46358</v>
       </c>
-      <c r="F51" s="7" t="n">
+      <c r="F51" s="31" t="n">
         <v>46364</v>
       </c>
       <c r="G51" s="5" t="inlineStr">
@@ -2802,6 +3008,9 @@
         <is>
           <t>THE security proof; gates waves</t>
         </is>
+      </c>
+      <c r="L51" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -2821,10 +3030,10 @@
       <c r="D52" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E52" s="10" t="n">
+      <c r="E52" s="33" t="n">
         <v>46358</v>
       </c>
-      <c r="F52" s="10" t="n">
+      <c r="F52" s="33" t="n">
         <v>46360</v>
       </c>
       <c r="G52" s="8" t="inlineStr">
@@ -2844,6 +3053,9 @@
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr"/>
+      <c r="L52" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
@@ -2862,10 +3074,10 @@
       <c r="D53" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E53" s="7" t="n">
+      <c r="E53" s="31" t="n">
         <v>46365</v>
       </c>
-      <c r="F53" s="7" t="n">
+      <c r="F53" s="31" t="n">
         <v>46367</v>
       </c>
       <c r="G53" s="5" t="inlineStr">
@@ -2881,6 +3093,9 @@
       </c>
       <c r="J53" s="6" t="inlineStr"/>
       <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
@@ -2899,10 +3114,10 @@
       <c r="D54" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E54" s="10" t="n">
+      <c r="E54" s="33" t="n">
         <v>46370</v>
       </c>
-      <c r="F54" s="10" t="n">
+      <c r="F54" s="33" t="n">
         <v>46409</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
@@ -2922,6 +3137,9 @@
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr"/>
+      <c r="L54" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="14" t="n">
@@ -2940,10 +3158,10 @@
       <c r="D55" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="E55" s="37" t="n">
         <v>46309</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="F55" s="37" t="n">
         <v>46311</v>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -2970,6 +3188,9 @@
         <is>
           <t>Slot pre-booked so execution beats the blackout</t>
         </is>
+      </c>
+      <c r="L55" s="38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -2989,10 +3210,10 @@
       <c r="D56" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="E56" s="37" t="n">
         <v>46358</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="F56" s="37" t="n">
         <v>46398</v>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -3019,6 +3240,9 @@
         <is>
           <t>Test env</t>
         </is>
+      </c>
+      <c r="L56" s="38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3038,10 +3262,10 @@
       <c r="D57" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E57" s="16" t="n">
+      <c r="E57" s="37" t="n">
         <v>46399</v>
       </c>
-      <c r="F57" s="16" t="n">
+      <c r="F57" s="37" t="n">
         <v>46413</v>
       </c>
       <c r="G57" s="14" t="inlineStr">
@@ -3065,6 +3289,9 @@
         </is>
       </c>
       <c r="K57" s="15" t="inlineStr"/>
+      <c r="L57" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="14" t="n">
@@ -3083,10 +3310,10 @@
       <c r="D58" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E58" s="16" t="n">
+      <c r="E58" s="37" t="n">
         <v>46414</v>
       </c>
-      <c r="F58" s="16" t="n">
+      <c r="F58" s="37" t="n">
         <v>46420</v>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -3110,6 +3337,9 @@
         </is>
       </c>
       <c r="K58" s="15" t="inlineStr"/>
+      <c r="L58" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="14" t="n">
@@ -3128,10 +3358,10 @@
       <c r="D59" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E59" s="16" t="n">
+      <c r="E59" s="37" t="n">
         <v>46421</v>
       </c>
-      <c r="F59" s="16" t="n">
+      <c r="F59" s="37" t="n">
         <v>46427</v>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -3155,6 +3385,9 @@
         </is>
       </c>
       <c r="K59" s="15" t="inlineStr"/>
+      <c r="L59" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="17" t="n">
@@ -3173,10 +3406,10 @@
       <c r="D60" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E60" s="19" t="n">
+      <c r="E60" s="39" t="n">
         <v>46428</v>
       </c>
-      <c r="F60" s="19" t="n">
+      <c r="F60" s="39" t="n">
         <v>46430</v>
       </c>
       <c r="G60" s="17" t="inlineStr">
@@ -3200,6 +3433,9 @@
         </is>
       </c>
       <c r="K60" s="18" t="inlineStr"/>
+      <c r="L60" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="n">
@@ -3218,10 +3454,10 @@
       <c r="D61" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E61" s="19" t="n">
+      <c r="E61" s="39" t="n">
         <v>46448</v>
       </c>
-      <c r="F61" s="19" t="n">
+      <c r="F61" s="39" t="n">
         <v>46448</v>
       </c>
       <c r="G61" s="17" t="inlineStr">
@@ -3241,6 +3477,9 @@
       </c>
       <c r="J61" s="18" t="inlineStr"/>
       <c r="K61" s="18" t="inlineStr"/>
+      <c r="L61" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="17" t="n">
@@ -3259,10 +3498,10 @@
       <c r="D62" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E62" s="19" t="n">
+      <c r="E62" s="39" t="n">
         <v>46449</v>
       </c>
-      <c r="F62" s="19" t="n">
+      <c r="F62" s="39" t="n">
         <v>46450</v>
       </c>
       <c r="G62" s="17" t="inlineStr">
@@ -3289,6 +3528,9 @@
         <is>
           <t>No prod changes 15-Dec-26 .. 08-Jan-27</t>
         </is>
+      </c>
+      <c r="L62" s="40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -3308,10 +3550,10 @@
       <c r="D63" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E63" s="7" t="n">
+      <c r="E63" s="31" t="n">
         <v>46451</v>
       </c>
-      <c r="F63" s="7" t="n">
+      <c r="F63" s="31" t="n">
         <v>46455</v>
       </c>
       <c r="G63" s="5" t="inlineStr">
@@ -3331,6 +3573,9 @@
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
+      <c r="L63" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
@@ -3349,10 +3594,10 @@
       <c r="D64" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E64" s="10" t="n">
+      <c r="E64" s="33" t="n">
         <v>46456</v>
       </c>
-      <c r="F64" s="10" t="n">
+      <c r="F64" s="33" t="n">
         <v>46458</v>
       </c>
       <c r="G64" s="8" t="inlineStr">
@@ -3372,6 +3617,9 @@
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr"/>
+      <c r="L64" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
@@ -3390,10 +3638,10 @@
       <c r="D65" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E65" s="7" t="n">
+      <c r="E65" s="31" t="n">
         <v>46461</v>
       </c>
-      <c r="F65" s="7" t="n">
+      <c r="F65" s="31" t="n">
         <v>46472</v>
       </c>
       <c r="G65" s="5" t="inlineStr">
@@ -3413,6 +3661,9 @@
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr"/>
+      <c r="L65" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
@@ -3431,10 +3682,10 @@
       <c r="D66" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E66" s="10" t="n">
+      <c r="E66" s="33" t="n">
         <v>46461</v>
       </c>
-      <c r="F66" s="10" t="n">
+      <c r="F66" s="33" t="n">
         <v>46472</v>
       </c>
       <c r="G66" s="8" t="inlineStr">
@@ -3454,6 +3705,9 @@
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr"/>
+      <c r="L66" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
@@ -3472,10 +3726,10 @@
       <c r="D67" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E67" s="7" t="n">
+      <c r="E67" s="31" t="n">
         <v>46475</v>
       </c>
-      <c r="F67" s="7" t="n">
+      <c r="F67" s="31" t="n">
         <v>46477</v>
       </c>
       <c r="G67" s="5" t="inlineStr">
@@ -3495,6 +3749,9 @@
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
+      <c r="L67" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="20" t="n">
@@ -3515,10 +3772,10 @@
           <t>0 — milestone</t>
         </is>
       </c>
-      <c r="E68" s="22" t="n">
+      <c r="E68" s="41" t="n">
         <v>46478</v>
       </c>
-      <c r="F68" s="22" t="n">
+      <c r="F68" s="41" t="n">
         <v>46478</v>
       </c>
       <c r="G68" s="20" t="inlineStr">
@@ -3534,6 +3791,9 @@
       </c>
       <c r="J68" s="21" t="inlineStr"/>
       <c r="K68" s="21" t="inlineStr"/>
+      <c r="L68" s="42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -3550,10 +3810,10 @@
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
-      <c r="E69" s="4" t="n">
+      <c r="E69" s="29" t="n">
         <v>46294</v>
       </c>
-      <c r="F69" s="4" t="n">
+      <c r="F69" s="29" t="n">
         <v>46499</v>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
@@ -3561,6 +3821,9 @@
       <c r="I69" s="3" t="inlineStr"/>
       <c r="J69" s="3" t="inlineStr"/>
       <c r="K69" s="3" t="inlineStr"/>
+      <c r="L69" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="11" t="n">
@@ -3579,10 +3842,10 @@
       <c r="D70" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E70" s="13" t="n">
+      <c r="E70" s="35" t="n">
         <v>46294</v>
       </c>
-      <c r="F70" s="13" t="n">
+      <c r="F70" s="35" t="n">
         <v>46315</v>
       </c>
       <c r="G70" s="11" t="inlineStr">
@@ -3606,6 +3869,9 @@
         </is>
       </c>
       <c r="K70" s="12" t="inlineStr"/>
+      <c r="L70" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="11" t="n">
@@ -3624,10 +3890,10 @@
       <c r="D71" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E71" s="13" t="n">
+      <c r="E71" s="35" t="n">
         <v>46323</v>
       </c>
-      <c r="F71" s="13" t="n">
+      <c r="F71" s="35" t="n">
         <v>46329</v>
       </c>
       <c r="G71" s="11" t="inlineStr">
@@ -3651,6 +3917,9 @@
         </is>
       </c>
       <c r="K71" s="12" t="inlineStr"/>
+      <c r="L71" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="11" t="n">
@@ -3669,10 +3938,10 @@
       <c r="D72" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E72" s="13" t="n">
+      <c r="E72" s="35" t="n">
         <v>46316</v>
       </c>
-      <c r="F72" s="13" t="n">
+      <c r="F72" s="35" t="n">
         <v>46322</v>
       </c>
       <c r="G72" s="11" t="inlineStr">
@@ -3696,6 +3965,9 @@
         </is>
       </c>
       <c r="K72" s="12" t="inlineStr"/>
+      <c r="L72" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
@@ -3714,10 +3986,10 @@
       <c r="D73" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E73" s="7" t="n">
+      <c r="E73" s="31" t="n">
         <v>46339</v>
       </c>
-      <c r="F73" s="7" t="n">
+      <c r="F73" s="31" t="n">
         <v>46353</v>
       </c>
       <c r="G73" s="5" t="inlineStr">
@@ -3737,6 +4009,9 @@
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr"/>
+      <c r="L73" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
@@ -3755,10 +4030,10 @@
       <c r="D74" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E74" s="10" t="n">
+      <c r="E74" s="33" t="n">
         <v>46356</v>
       </c>
-      <c r="F74" s="10" t="n">
+      <c r="F74" s="33" t="n">
         <v>46360</v>
       </c>
       <c r="G74" s="8" t="inlineStr">
@@ -3778,6 +4053,9 @@
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr"/>
+      <c r="L74" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="14" t="n">
@@ -3796,10 +4074,10 @@
       <c r="D75" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E75" s="16" t="n">
+      <c r="E75" s="37" t="n">
         <v>46363</v>
       </c>
-      <c r="F75" s="16" t="n">
+      <c r="F75" s="37" t="n">
         <v>46401</v>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -3819,6 +4097,9 @@
       </c>
       <c r="J75" s="15" t="inlineStr"/>
       <c r="K75" s="15" t="inlineStr"/>
+      <c r="L75" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="17" t="n">
@@ -3837,10 +4118,10 @@
       <c r="D76" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E76" s="19" t="n">
+      <c r="E76" s="39" t="n">
         <v>46456</v>
       </c>
-      <c r="F76" s="19" t="n">
+      <c r="F76" s="39" t="n">
         <v>46458</v>
       </c>
       <c r="G76" s="17" t="inlineStr">
@@ -3867,6 +4148,9 @@
         <is>
           <t>Gated on pilot deploy success</t>
         </is>
+      </c>
+      <c r="L76" s="40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -3886,10 +4170,10 @@
       <c r="D77" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="19" t="n">
+      <c r="E77" s="39" t="n">
         <v>46475</v>
       </c>
-      <c r="F77" s="19" t="n">
+      <c r="F77" s="39" t="n">
         <v>46475</v>
       </c>
       <c r="G77" s="17" t="inlineStr">
@@ -3909,6 +4193,9 @@
       </c>
       <c r="J77" s="18" t="inlineStr"/>
       <c r="K77" s="18" t="inlineStr"/>
+      <c r="L77" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
@@ -3927,10 +4214,10 @@
       <c r="D78" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E78" s="10" t="n">
+      <c r="E78" s="33" t="n">
         <v>46476</v>
       </c>
-      <c r="F78" s="10" t="n">
+      <c r="F78" s="33" t="n">
         <v>46482</v>
       </c>
       <c r="G78" s="8" t="inlineStr">
@@ -3950,6 +4237,9 @@
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr"/>
+      <c r="L78" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="n">
@@ -3968,10 +4258,10 @@
       <c r="D79" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E79" s="7" t="n">
+      <c r="E79" s="31" t="n">
         <v>46483</v>
       </c>
-      <c r="F79" s="7" t="n">
+      <c r="F79" s="31" t="n">
         <v>46484</v>
       </c>
       <c r="G79" s="5" t="inlineStr">
@@ -3991,6 +4281,9 @@
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr"/>
+      <c r="L79" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
@@ -4009,10 +4302,10 @@
       <c r="D80" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E80" s="10" t="n">
+      <c r="E80" s="33" t="n">
         <v>46485</v>
       </c>
-      <c r="F80" s="10" t="n">
+      <c r="F80" s="33" t="n">
         <v>46498</v>
       </c>
       <c r="G80" s="8" t="inlineStr">
@@ -4032,6 +4325,9 @@
         </is>
       </c>
       <c r="K80" s="9" t="inlineStr"/>
+      <c r="L80" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="20" t="n">
@@ -4052,10 +4348,10 @@
           <t>0 — milestone</t>
         </is>
       </c>
-      <c r="E81" s="22" t="n">
+      <c r="E81" s="41" t="n">
         <v>46499</v>
       </c>
-      <c r="F81" s="22" t="n">
+      <c r="F81" s="41" t="n">
         <v>46499</v>
       </c>
       <c r="G81" s="20" t="inlineStr">
@@ -4071,6 +4367,9 @@
       </c>
       <c r="J81" s="21" t="inlineStr"/>
       <c r="K81" s="21" t="inlineStr"/>
+      <c r="L81" s="42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="n">
@@ -4089,10 +4388,10 @@
       <c r="D82" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E82" s="35" t="n">
         <v>46294</v>
       </c>
-      <c r="F82" s="13" t="n">
+      <c r="F82" s="35" t="n">
         <v>46315</v>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -4116,6 +4415,9 @@
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr"/>
+      <c r="L82" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="n">
@@ -4134,10 +4436,10 @@
       <c r="D83" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="13" t="n">
+      <c r="E83" s="35" t="n">
         <v>46316</v>
       </c>
-      <c r="F83" s="13" t="n">
+      <c r="F83" s="35" t="n">
         <v>46322</v>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -4161,6 +4463,9 @@
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr"/>
+      <c r="L83" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="11" t="n">
@@ -4179,10 +4484,10 @@
       <c r="D84" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E84" s="13" t="n">
+      <c r="E84" s="35" t="n">
         <v>46316</v>
       </c>
-      <c r="F84" s="13" t="n">
+      <c r="F84" s="35" t="n">
         <v>46329</v>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -4209,6 +4514,9 @@
         <is>
           <t>filters.json is change-controlled</t>
         </is>
+      </c>
+      <c r="L84" s="36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -4228,10 +4536,10 @@
       <c r="D85" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E85" s="7" t="n">
+      <c r="E85" s="31" t="n">
         <v>46316</v>
       </c>
-      <c r="F85" s="7" t="n">
+      <c r="F85" s="31" t="n">
         <v>46318</v>
       </c>
       <c r="G85" s="5" t="inlineStr">
@@ -4250,6 +4558,9 @@
         <is>
           <t>Item id = Salesforce record Id</t>
         </is>
+      </c>
+      <c r="L85" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -4269,10 +4580,10 @@
       <c r="D86" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E86" s="10" t="n">
+      <c r="E86" s="33" t="n">
         <v>46339</v>
       </c>
-      <c r="F86" s="10" t="n">
+      <c r="F86" s="33" t="n">
         <v>46345</v>
       </c>
       <c r="G86" s="8" t="inlineStr">
@@ -4292,6 +4603,9 @@
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr"/>
+      <c r="L86" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
@@ -4310,10 +4624,10 @@
       <c r="D87" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E87" s="7" t="n">
+      <c r="E87" s="31" t="n">
         <v>46346</v>
       </c>
-      <c r="F87" s="7" t="n">
+      <c r="F87" s="31" t="n">
         <v>46360</v>
       </c>
       <c r="G87" s="5" t="inlineStr">
@@ -4333,6 +4647,9 @@
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr"/>
+      <c r="L87" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="8" t="n">
@@ -4351,10 +4668,10 @@
       <c r="D88" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E88" s="10" t="n">
+      <c r="E88" s="33" t="n">
         <v>46363</v>
       </c>
-      <c r="F88" s="10" t="n">
+      <c r="F88" s="33" t="n">
         <v>46367</v>
       </c>
       <c r="G88" s="8" t="inlineStr">
@@ -4374,6 +4691,9 @@
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr"/>
+      <c r="L88" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="14" t="n">
@@ -4392,10 +4712,10 @@
       <c r="D89" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E89" s="16" t="n">
+      <c r="E89" s="37" t="n">
         <v>46370</v>
       </c>
-      <c r="F89" s="16" t="n">
+      <c r="F89" s="37" t="n">
         <v>46409</v>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -4415,6 +4735,9 @@
       </c>
       <c r="J89" s="15" t="inlineStr"/>
       <c r="K89" s="15" t="inlineStr"/>
+      <c r="L89" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="17" t="n">
@@ -4433,10 +4756,10 @@
       <c r="D90" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="19" t="n">
+      <c r="E90" s="39" t="n">
         <v>46456</v>
       </c>
-      <c r="F90" s="19" t="n">
+      <c r="F90" s="39" t="n">
         <v>46458</v>
       </c>
       <c r="G90" s="17" t="inlineStr">
@@ -4460,6 +4783,9 @@
         </is>
       </c>
       <c r="K90" s="18" t="inlineStr"/>
+      <c r="L90" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="17" t="n">
@@ -4478,10 +4804,10 @@
       <c r="D91" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E91" s="19" t="n">
+      <c r="E91" s="39" t="n">
         <v>46475</v>
       </c>
-      <c r="F91" s="19" t="n">
+      <c r="F91" s="39" t="n">
         <v>46475</v>
       </c>
       <c r="G91" s="17" t="inlineStr">
@@ -4501,6 +4827,9 @@
       </c>
       <c r="J91" s="18" t="inlineStr"/>
       <c r="K91" s="18" t="inlineStr"/>
+      <c r="L91" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="8" t="n">
@@ -4519,10 +4848,10 @@
       <c r="D92" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E92" s="10" t="n">
+      <c r="E92" s="33" t="n">
         <v>46476</v>
       </c>
-      <c r="F92" s="10" t="n">
+      <c r="F92" s="33" t="n">
         <v>46482</v>
       </c>
       <c r="G92" s="8" t="inlineStr">
@@ -4542,6 +4871,9 @@
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr"/>
+      <c r="L92" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
@@ -4560,10 +4892,10 @@
       <c r="D93" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E93" s="7" t="n">
+      <c r="E93" s="31" t="n">
         <v>46483</v>
       </c>
-      <c r="F93" s="7" t="n">
+      <c r="F93" s="31" t="n">
         <v>46484</v>
       </c>
       <c r="G93" s="5" t="inlineStr">
@@ -4583,6 +4915,9 @@
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr"/>
+      <c r="L93" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="8" t="n">
@@ -4601,10 +4936,10 @@
       <c r="D94" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E94" s="10" t="n">
+      <c r="E94" s="33" t="n">
         <v>46485</v>
       </c>
-      <c r="F94" s="10" t="n">
+      <c r="F94" s="33" t="n">
         <v>46498</v>
       </c>
       <c r="G94" s="8" t="inlineStr">
@@ -4624,6 +4959,9 @@
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr"/>
+      <c r="L94" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="n">
@@ -4644,10 +4982,10 @@
           <t>0 — milestone</t>
         </is>
       </c>
-      <c r="E95" s="22" t="n">
+      <c r="E95" s="41" t="n">
         <v>46499</v>
       </c>
-      <c r="F95" s="22" t="n">
+      <c r="F95" s="41" t="n">
         <v>46499</v>
       </c>
       <c r="G95" s="20" t="inlineStr">
@@ -4663,6 +5001,9 @@
       </c>
       <c r="J95" s="21" t="inlineStr"/>
       <c r="K95" s="21" t="inlineStr"/>
+      <c r="L95" s="42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -4679,10 +5020,10 @@
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
-      <c r="E96" s="4" t="n">
+      <c r="E96" s="29" t="n">
         <v>46287</v>
       </c>
-      <c r="F96" s="4" t="n">
+      <c r="F96" s="29" t="n">
         <v>46497</v>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
@@ -4690,6 +5031,9 @@
       <c r="I96" s="3" t="inlineStr"/>
       <c r="J96" s="3" t="inlineStr"/>
       <c r="K96" s="3" t="inlineStr"/>
+      <c r="L96" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="14" t="n">
@@ -4708,10 +5052,10 @@
       <c r="D97" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="E97" s="16" t="n">
+      <c r="E97" s="37" t="n">
         <v>46287</v>
       </c>
-      <c r="F97" s="16" t="n">
+      <c r="F97" s="37" t="n">
         <v>46322</v>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -4735,6 +5079,9 @@
         </is>
       </c>
       <c r="K97" s="15" t="inlineStr"/>
+      <c r="L97" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="n">
@@ -4753,10 +5100,10 @@
       <c r="D98" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E98" s="16" t="n">
+      <c r="E98" s="37" t="n">
         <v>46323</v>
       </c>
-      <c r="F98" s="16" t="n">
+      <c r="F98" s="37" t="n">
         <v>46336</v>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -4783,6 +5130,9 @@
         <is>
           <t>Gate for all Altrata prod work</t>
         </is>
+      </c>
+      <c r="L98" s="38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="99">
@@ -4802,10 +5152,10 @@
       <c r="D99" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="E99" s="13" t="n">
+      <c r="E99" s="35" t="n">
         <v>46294</v>
       </c>
-      <c r="F99" s="13" t="n">
+      <c r="F99" s="35" t="n">
         <v>46315</v>
       </c>
       <c r="G99" s="11" t="inlineStr">
@@ -4829,6 +5179,9 @@
         </is>
       </c>
       <c r="K99" s="12" t="inlineStr"/>
+      <c r="L99" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="n">
@@ -4847,10 +5200,10 @@
       <c r="D100" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E100" s="13" t="n">
+      <c r="E100" s="35" t="n">
         <v>46316</v>
       </c>
-      <c r="F100" s="13" t="n">
+      <c r="F100" s="35" t="n">
         <v>46329</v>
       </c>
       <c r="G100" s="11" t="inlineStr">
@@ -4874,6 +5227,9 @@
         </is>
       </c>
       <c r="K100" s="12" t="inlineStr"/>
+      <c r="L100" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="n">
@@ -4892,10 +5248,10 @@
       <c r="D101" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E101" s="7" t="n">
+      <c r="E101" s="31" t="n">
         <v>46330</v>
       </c>
-      <c r="F101" s="7" t="n">
+      <c r="F101" s="31" t="n">
         <v>46332</v>
       </c>
       <c r="G101" s="5" t="inlineStr">
@@ -4918,6 +5274,9 @@
         <is>
           <t>RPO-0 backup tier</t>
         </is>
+      </c>
+      <c r="L101" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -4937,10 +5296,10 @@
       <c r="D102" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E102" s="10" t="n">
+      <c r="E102" s="33" t="n">
         <v>46339</v>
       </c>
-      <c r="F102" s="10" t="n">
+      <c r="F102" s="33" t="n">
         <v>46353</v>
       </c>
       <c r="G102" s="8" t="inlineStr">
@@ -4960,6 +5319,9 @@
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr"/>
+      <c r="L102" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="n">
@@ -4978,10 +5340,10 @@
       <c r="D103" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E103" s="7" t="n">
+      <c r="E103" s="31" t="n">
         <v>46356</v>
       </c>
-      <c r="F103" s="7" t="n">
+      <c r="F103" s="31" t="n">
         <v>46360</v>
       </c>
       <c r="G103" s="5" t="inlineStr">
@@ -5001,6 +5363,9 @@
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr"/>
+      <c r="L103" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="n">
@@ -5019,10 +5384,10 @@
       <c r="D104" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E104" s="10" t="n">
+      <c r="E104" s="33" t="n">
         <v>46363</v>
       </c>
-      <c r="F104" s="10" t="n">
+      <c r="F104" s="33" t="n">
         <v>46367</v>
       </c>
       <c r="G104" s="8" t="inlineStr">
@@ -5042,6 +5407,9 @@
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr"/>
+      <c r="L104" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="14" t="n">
@@ -5060,10 +5428,10 @@
       <c r="D105" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="E105" s="16" t="n">
+      <c r="E105" s="37" t="n">
         <v>46370</v>
       </c>
-      <c r="F105" s="16" t="n">
+      <c r="F105" s="37" t="n">
         <v>46409</v>
       </c>
       <c r="G105" s="14" t="inlineStr">
@@ -5087,6 +5455,9 @@
         </is>
       </c>
       <c r="K105" s="15" t="inlineStr"/>
+      <c r="L105" s="38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="17" t="n">
@@ -5105,10 +5476,10 @@
       <c r="D106" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E106" s="19" t="n">
+      <c r="E106" s="39" t="n">
         <v>46456</v>
       </c>
-      <c r="F106" s="19" t="n">
+      <c r="F106" s="39" t="n">
         <v>46458</v>
       </c>
       <c r="G106" s="17" t="inlineStr">
@@ -5132,6 +5503,9 @@
         </is>
       </c>
       <c r="K106" s="18" t="inlineStr"/>
+      <c r="L106" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="17" t="n">
@@ -5150,10 +5524,10 @@
       <c r="D107" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E107" s="19" t="n">
+      <c r="E107" s="39" t="n">
         <v>46475</v>
       </c>
-      <c r="F107" s="19" t="n">
+      <c r="F107" s="39" t="n">
         <v>46475</v>
       </c>
       <c r="G107" s="17" t="inlineStr">
@@ -5173,6 +5547,9 @@
       </c>
       <c r="J107" s="18" t="inlineStr"/>
       <c r="K107" s="18" t="inlineStr"/>
+      <c r="L107" s="40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="n">
@@ -5191,10 +5568,10 @@
       <c r="D108" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E108" s="10" t="n">
+      <c r="E108" s="33" t="n">
         <v>46476</v>
       </c>
-      <c r="F108" s="10" t="n">
+      <c r="F108" s="33" t="n">
         <v>46482</v>
       </c>
       <c r="G108" s="8" t="inlineStr">
@@ -5214,6 +5591,9 @@
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr"/>
+      <c r="L108" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="n">
@@ -5232,10 +5612,10 @@
       <c r="D109" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E109" s="7" t="n">
+      <c r="E109" s="31" t="n">
         <v>46370</v>
       </c>
-      <c r="F109" s="7" t="n">
+      <c r="F109" s="31" t="n">
         <v>46401</v>
       </c>
       <c r="G109" s="5" t="inlineStr">
@@ -5255,6 +5635,9 @@
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr"/>
+      <c r="L109" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="n">
@@ -5273,10 +5656,10 @@
       <c r="D110" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E110" s="10" t="n">
+      <c r="E110" s="33" t="n">
         <v>46483</v>
       </c>
-      <c r="F110" s="10" t="n">
+      <c r="F110" s="33" t="n">
         <v>46496</v>
       </c>
       <c r="G110" s="8" t="inlineStr">
@@ -5296,6 +5679,9 @@
         </is>
       </c>
       <c r="K110" s="9" t="inlineStr"/>
+      <c r="L110" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="20" t="n">
@@ -5316,10 +5702,10 @@
           <t>0 — milestone</t>
         </is>
       </c>
-      <c r="E111" s="22" t="n">
+      <c r="E111" s="41" t="n">
         <v>46497</v>
       </c>
-      <c r="F111" s="22" t="n">
+      <c r="F111" s="41" t="n">
         <v>46497</v>
       </c>
       <c r="G111" s="20" t="inlineStr">
@@ -5335,6 +5721,9 @@
       </c>
       <c r="J111" s="21" t="inlineStr"/>
       <c r="K111" s="21" t="inlineStr"/>
+      <c r="L111" s="42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -5351,10 +5740,10 @@
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
-      <c r="E112" s="4" t="n">
+      <c r="E112" s="29" t="n">
         <v>46339</v>
       </c>
-      <c r="F112" s="4" t="n">
+      <c r="F112" s="29" t="n">
         <v>46492</v>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
@@ -5362,6 +5751,9 @@
       <c r="I112" s="3" t="inlineStr"/>
       <c r="J112" s="3" t="inlineStr"/>
       <c r="K112" s="3" t="inlineStr"/>
+      <c r="L112" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
@@ -5380,10 +5772,10 @@
       <c r="D113" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="E113" s="7" t="n">
+      <c r="E113" s="31" t="n">
         <v>46339</v>
       </c>
-      <c r="F113" s="7" t="n">
+      <c r="F113" s="31" t="n">
         <v>46353</v>
       </c>
       <c r="G113" s="5" t="inlineStr">
@@ -5403,6 +5795,9 @@
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr"/>
+      <c r="L113" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="8" t="n">
@@ -5421,10 +5816,10 @@
       <c r="D114" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E114" s="10" t="n">
+      <c r="E114" s="33" t="n">
         <v>46479</v>
       </c>
-      <c r="F114" s="10" t="n">
+      <c r="F114" s="33" t="n">
         <v>46485</v>
       </c>
       <c r="G114" s="8" t="inlineStr">
@@ -5444,6 +5839,9 @@
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr"/>
+      <c r="L114" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
@@ -5462,10 +5860,10 @@
       <c r="D115" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E115" s="7" t="n">
+      <c r="E115" s="31" t="n">
         <v>46479</v>
       </c>
-      <c r="F115" s="7" t="n">
+      <c r="F115" s="31" t="n">
         <v>46485</v>
       </c>
       <c r="G115" s="5" t="inlineStr">
@@ -5488,6 +5886,9 @@
         <is>
           <t>Altrata strict tier</t>
         </is>
+      </c>
+      <c r="L115" s="32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5507,10 +5908,10 @@
       <c r="D116" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="E116" s="10" t="n">
+      <c r="E116" s="33" t="n">
         <v>46479</v>
       </c>
-      <c r="F116" s="10" t="n">
+      <c r="F116" s="33" t="n">
         <v>46492</v>
       </c>
       <c r="G116" s="8" t="inlineStr">
@@ -5530,6 +5931,9 @@
         </is>
       </c>
       <c r="K116" s="9" t="inlineStr"/>
+      <c r="L116" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
@@ -5548,10 +5952,10 @@
       <c r="D117" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E117" s="7" t="n">
+      <c r="E117" s="31" t="n">
         <v>46356</v>
       </c>
-      <c r="F117" s="7" t="n">
+      <c r="F117" s="31" t="n">
         <v>46358</v>
       </c>
       <c r="G117" s="5" t="inlineStr">
@@ -5571,6 +5975,9 @@
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr"/>
+      <c r="L117" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
@@ -5587,10 +5994,10 @@
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="4" t="n">
+      <c r="E118" s="29" t="n">
         <v>46479</v>
       </c>
-      <c r="F118" s="4" t="n">
+      <c r="F118" s="29" t="n">
         <v>46535</v>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
@@ -5598,6 +6005,9 @@
       <c r="I118" s="3" t="inlineStr"/>
       <c r="J118" s="3" t="inlineStr"/>
       <c r="K118" s="3" t="inlineStr"/>
+      <c r="L118" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="n">
@@ -5616,10 +6026,10 @@
       <c r="D119" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="E119" s="13" t="n">
+      <c r="E119" s="35" t="n">
         <v>46479</v>
       </c>
-      <c r="F119" s="13" t="n">
+      <c r="F119" s="35" t="n">
         <v>46492</v>
       </c>
       <c r="G119" s="11" t="inlineStr">
@@ -5643,6 +6053,9 @@
         </is>
       </c>
       <c r="K119" s="12" t="inlineStr"/>
+      <c r="L119" s="36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="8" t="n">
@@ -5661,10 +6074,10 @@
       <c r="D120" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="E120" s="10" t="n">
+      <c r="E120" s="33" t="n">
         <v>46521</v>
       </c>
-      <c r="F120" s="10" t="n">
+      <c r="F120" s="33" t="n">
         <v>46527</v>
       </c>
       <c r="G120" s="8" t="inlineStr">
@@ -5684,6 +6097,9 @@
         </is>
       </c>
       <c r="K120" s="9" t="inlineStr"/>
+      <c r="L120" s="34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
@@ -5702,10 +6118,10 @@
       <c r="D121" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E121" s="7" t="n">
+      <c r="E121" s="31" t="n">
         <v>46528</v>
       </c>
-      <c r="F121" s="7" t="n">
+      <c r="F121" s="31" t="n">
         <v>46532</v>
       </c>
       <c r="G121" s="5" t="inlineStr">
@@ -5725,6 +6141,9 @@
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr"/>
+      <c r="L121" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="8" t="n">
@@ -5743,10 +6162,10 @@
       <c r="D122" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E122" s="10" t="n">
+      <c r="E122" s="33" t="n">
         <v>46528</v>
       </c>
-      <c r="F122" s="10" t="n">
+      <c r="F122" s="33" t="n">
         <v>46531</v>
       </c>
       <c r="G122" s="8" t="inlineStr">
@@ -5769,6 +6188,9 @@
         <is>
           <t>Built + tested; deploy only if live-CRM freshness is needed</t>
         </is>
+      </c>
+      <c r="L122" s="34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -5788,10 +6210,10 @@
       <c r="D123" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E123" s="7" t="n">
+      <c r="E123" s="31" t="n">
         <v>46528</v>
       </c>
-      <c r="F123" s="7" t="n">
+      <c r="F123" s="31" t="n">
         <v>46534</v>
       </c>
       <c r="G123" s="5" t="inlineStr">
@@ -5811,6 +6233,9 @@
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr"/>
+      <c r="L123" s="32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="n">
@@ -5831,10 +6256,10 @@
           <t>0 — milestone</t>
         </is>
       </c>
-      <c r="E124" s="22" t="n">
+      <c r="E124" s="41" t="n">
         <v>46535</v>
       </c>
-      <c r="F124" s="22" t="n">
+      <c r="F124" s="41" t="n">
         <v>46535</v>
       </c>
       <c r="G124" s="20" t="inlineStr">
@@ -5854,9 +6279,524 @@
         </is>
       </c>
       <c r="K124" s="21" t="inlineStr"/>
+      <c r="L124" s="42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>ENGINEERING BASELINE — shared-chassis consolidation delivered on main (pre-Phase 0)</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n"/>
+      <c r="E125" s="29" t="n">
+        <v>46245</v>
+      </c>
+      <c r="F125" s="29" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G125" s="2" t="n"/>
+      <c r="H125" s="2" t="n"/>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="3" t="n"/>
+      <c r="K125" s="3" t="inlineStr">
+        <is>
+          <t>Delivered before mobilisation; appended so Phase 0-4 IDs and predecessors are unchanged</t>
+        </is>
+      </c>
+      <c r="L125" s="30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="5" t="inlineStr">
+        <is>
+          <t>8.1</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Connector.Chassis landed as a single top-level project (now v1.18.0)</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E126" s="31" t="n">
+        <v>46245</v>
+      </c>
+      <c r="F126" s="31" t="n">
+        <v>46245</v>
+      </c>
+      <c r="G126" s="5" t="n"/>
+      <c r="H126" s="5" t="n"/>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="n"/>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>One project at the repository root; chassis.yml builds and packs it (testing added 14-Aug-26 — see 8.7)</t>
+        </is>
+      </c>
+      <c r="L126" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="5" t="inlineStr">
+        <is>
+          <t>8.2</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    All five connectors switched to ProjectReference on the shared chassis</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E127" s="31" t="n">
+        <v>46245</v>
+      </c>
+      <c r="F127" s="31" t="n">
+        <v>46246</v>
+      </c>
+      <c r="G127" s="5" t="n"/>
+      <c r="H127" s="5" t="n"/>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J127" s="6" t="n"/>
+      <c r="K127" s="6" t="inlineStr">
+        <is>
+          <t>Seismic, Clarizen, Hadoop 11-Aug-26; Salesforce, Altrata 12-Aug-26. ProjectReference to one project on disk — never a package, never a copy</t>
+        </is>
+      </c>
+      <c r="L127" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="5" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Root CI: 8 workflows — five connectors, chassis, conformance, CodeQL</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" s="31" t="n">
+        <v>46245</v>
+      </c>
+      <c r="F128" s="31" t="n">
+        <v>46247</v>
+      </c>
+      <c r="G128" s="5" t="n"/>
+      <c r="H128" s="5" t="n"/>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="n"/>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>Build + test on ubuntu-latest AND windows-latest, plus a non-pushed Docker build per connector. Per-connector .github/ workflows are inert — GitHub runs root workflows only</t>
+        </is>
+      </c>
+      <c r="L128" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Conformance gate resolves the ProjectReference and asserts the register</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F129" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G129" s="5" t="n"/>
+      <c r="H129" s="5" t="n"/>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="n"/>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>conformance.yml self-tests, then asserts capabilities and the divergence register on every PR</t>
+        </is>
+      </c>
+      <c r="L129" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Divergence register in force — 9 of 23 modules shared, 67 declared copies</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E130" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F130" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G130" s="5" t="n"/>
+      <c r="H130" s="5" t="n"/>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J130" s="6" t="n"/>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>Salesforce 22, Clarizen 16, Hadoop 16, Altrata 13, Seismic 0, plus 9 renamed equivalents recorded. A ratchet: CI fails on an undeclared copy and on a register line whose copy no longer exists</t>
+        </is>
+      </c>
+      <c r="L130" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>8.6</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Alerting consolidated onto the chassis — 4 of the 5 connectors</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E131" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F131" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G131" s="5" t="n"/>
+      <c r="H131" s="5" t="n"/>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J131" s="6" t="n"/>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>Clarizen, Hadoop and Salesforce joined Seismic. Altrata keeps its own, declared: its alert payload is an operator-facing contract SIEM routing keys on</t>
+        </is>
+      </c>
+      <c r="L131" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>8.7</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Chassis given its own test suite — 558 tests</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E132" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F132" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G132" s="5" t="n"/>
+      <c r="H132" s="5" t="n"/>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J132" s="6" t="n"/>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>chassis.yml now tests as well as builds and packs, on both operating systems</t>
+        </is>
+      </c>
+      <c r="L132" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>8.8</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Environment-flag parsing unified across the fleet</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E133" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F133" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G133" s="5" t="n"/>
+      <c r="H133" s="5" t="n"/>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J133" s="6" t="n"/>
+      <c r="K133" s="6" t="inlineStr">
+        <is>
+          <t>One boolean vocabulary; a mistyped value can no longer silently flip a gate</t>
+        </is>
+      </c>
+      <c r="L133" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Altrata decision ledger — single-byte separator tamper now detected</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E134" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F134" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G134" s="5" t="n"/>
+      <c r="H134" s="5" t="n"/>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J134" s="6" t="n"/>
+      <c r="K134" s="6" t="n"/>
+      <c r="L134" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>8.10</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Fleet suite green on both operating systems — 5,445 tests, 0 skipped</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E135" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F135" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G135" s="5" t="n"/>
+      <c r="H135" s="5" t="n"/>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>QA/Test Engineer</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="n"/>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>Chassis 558, Salesforce 1,213, Seismic 1,025, Hadoop 988, Clarizen 897, Altrata 764. Identical counts on ubuntu-latest and windows-latest</t>
+        </is>
+      </c>
+      <c r="L135" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="5" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>8.11</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Repository controls: branch protection on main + Dependabot security alerts</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E136" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F136" s="31" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G136" s="5" t="n"/>
+      <c r="H136" s="5" t="n"/>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="n"/>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>Both enabled 14-Aug-26. CodeQL analyses six solutions and reports ~2,029 open alerts, but gates nothing</t>
+        </is>
+      </c>
+      <c r="L136" s="32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="20" t="inlineStr">
+        <is>
+          <t>8.12</t>
+        </is>
+      </c>
+      <c r="C137" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    MILESTONE — shared-chassis consolidation complete on main (e138f11)</t>
+        </is>
+      </c>
+      <c r="D137" s="20" t="inlineStr">
+        <is>
+          <t>0 — milestone</t>
+        </is>
+      </c>
+      <c r="E137" s="41" t="n">
+        <v>46248</v>
+      </c>
+      <c r="F137" s="41" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G137" s="20" t="n"/>
+      <c r="H137" s="20" t="n"/>
+      <c r="I137" s="21" t="inlineStr">
+        <is>
+          <t>Platform Lead &amp; Architect</t>
+        </is>
+      </c>
+      <c r="J137" s="21" t="n"/>
+      <c r="K137" s="21" t="inlineStr">
+        <is>
+          <t>Out of scope of this milestone and still open: release pipeline at the repository root (2.19); TOGAF concerns 3-7 (2.20); 67 declared divergences to retire</t>
+        </is>
+      </c>
+      <c r="L137" s="42" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K124"/>
+  <autoFilter ref="A1:L137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5867,7 +6807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -5890,7 +6830,7 @@
       </c>
       <c r="B2" s="24" t="inlineStr">
         <is>
-          <t>17 Aug 2026</t>
+          <t>17 Aug 2026 (Phase 0 mobilisation). The delivered engineering baseline in section 8 ran 11-14 Aug 2026, ahead of it.</t>
         </is>
       </c>
     </row>
@@ -6032,6 +6972,30 @@
       <c r="A15" s="28" t="inlineStr">
         <is>
           <t>CAB / CHANGE example</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="inlineStr">
+        <is>
+          <t>Status at 14 Aug 2026</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>The programme itself has not started — every Phase 0-4 task is 0% complete. Section 8 records the engineering work already delivered on main at commit e138f11: ONE shared Connector.Chassis project (v1.18.0) consumed by all five connectors via ProjectReference and asserted on every PR by .github/workflows/conformance.yml. Shared does not mean uniform: 9 of 23 chassis modules are fully shared and 67 per-connector copies remain, each declared in .github/conformance/divergences.tsv and enforced as a ratchet. Fleet regression suite 5,445 tests, 0 skipped, identical on ubuntu-latest and windows-latest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="inlineStr">
+        <is>
+          <t>Not yet delivered</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>No release pipeline exists at the repository root and no release or tag has ever been produced; the SBOM / Authenticode / cosign / MSI designs sit in five per-connector workflow files GitHub never runs (task 2.19 builds the real thing). TOGAF concerns 3-7 remain open (task 2.20). CodeQL runs but gates nothing. Branch protection on main and Dependabot security alerts were only switched on 14 Aug 2026.</t>
         </is>
       </c>
     </row>
